--- a/docs/download/training-tracker-template.xlsx
+++ b/docs/download/training-tracker-template.xlsx
@@ -5,6 +5,8 @@
     <sheet name="Log" sheetId="1" r:id="rId1"/>
     <sheet name="Exercises" sheetId="2" r:id="rId2"/>
     <sheet name="Templates" sheetId="3" r:id="rId3"/>
+    <sheet name="Settings" sheetId="4" r:id="rId4"/>
+    <sheet name="Records" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -82,28 +84,33 @@
           <t xml:space="preserve">pattern</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">image</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbell Bench Press</t>
+          <t xml:space="preserve">[Other]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chest</t>
+          <t xml:space="preserve">Placeholder</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Push</t>
+          <t xml:space="preserve">Any</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incline Barbell Bench Press</t>
+          <t xml:space="preserve">Barbell Bench Press</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -120,7 +127,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dumbbell Bench Press</t>
+          <t xml:space="preserve">Incline Barbell Bench Press</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -137,7 +144,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incline Dumbbell Press</t>
+          <t xml:space="preserve">Decline Barbell Bench Press</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -154,7 +161,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine Chest Press</t>
+          <t xml:space="preserve">Dumbbell Bench Press</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -171,7 +178,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Chest Fly</t>
+          <t xml:space="preserve">Incline Dumbbell Press</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -188,7 +195,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pec Deck</t>
+          <t xml:space="preserve">Decline Dumbbell Press</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -205,7 +212,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Push-Up</t>
+          <t xml:space="preserve">Machine Chest Press</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -222,7 +229,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dip</t>
+          <t xml:space="preserve">Incline Machine Press</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -239,12 +246,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overhead Barbell Press</t>
+          <t xml:space="preserve">Smith Machine Bench Press</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shoulders</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -256,12 +263,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seated Dumbbell Shoulder Press</t>
+          <t xml:space="preserve">Floor Press</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shoulders</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -273,12 +280,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnold Press</t>
+          <t xml:space="preserve">Pin Press</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shoulders</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -290,12 +297,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lateral Raise</t>
+          <t xml:space="preserve">Board Press</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shoulders</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -307,12 +314,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Lateral Raise</t>
+          <t xml:space="preserve">Spoto Press</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shoulders</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -324,12 +331,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Front Raise</t>
+          <t xml:space="preserve">Cable Chest Fly</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shoulders</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -341,12 +348,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triceps Rope Pushdown</t>
+          <t xml:space="preserve">Low-to-High Cable Fly</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triceps</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -358,12 +365,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triceps Cable Pushdown</t>
+          <t xml:space="preserve">High-to-Low Cable Fly</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triceps</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -375,12 +382,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skull Crusher</t>
+          <t xml:space="preserve">Dumbbell Fly</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triceps</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -392,12 +399,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overhead Triceps Extension</t>
+          <t xml:space="preserve">Incline Dumbbell Fly</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triceps</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -409,12 +416,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Close-Grip Bench Press</t>
+          <t xml:space="preserve">Pec Deck</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triceps</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -426,816 +433,4012 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deadlift</t>
+          <t xml:space="preserve">Svend Press</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbell Row</t>
+          <t xml:space="preserve">Push-Up</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pendlay Row</t>
+          <t xml:space="preserve">Incline Push-Up</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dumbbell Row</t>
+          <t xml:space="preserve">Decline Push-Up</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chest-Supported Row</t>
+          <t xml:space="preserve">Diamond Push-Up</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seated Cable Row</t>
+          <t xml:space="preserve">Deficit Push-Up</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lat Pulldown</t>
+          <t xml:space="preserve">Chest Dip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wide-Grip Lat Pulldown</t>
+          <t xml:space="preserve">Ring Dip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Straight-Arm Pulldown</t>
+          <t xml:space="preserve">Overhead Barbell Press</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull-Up</t>
+          <t xml:space="preserve">Seated Barbell Shoulder Press</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chin-Up</t>
+          <t xml:space="preserve">Push Press</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assisted Pull-Up</t>
+          <t xml:space="preserve">Push Jerk</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">T-Bar Row</t>
+          <t xml:space="preserve">Seated Dumbbell Shoulder Press</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Face Pull</t>
+          <t xml:space="preserve">Standing Dumbbell Shoulder Press</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rear delts</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reverse Pec Deck</t>
+          <t xml:space="preserve">Arnold Press</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rear delts</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbell Shrug</t>
+          <t xml:space="preserve">Machine Shoulder Press</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Traps</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dumbbell Shrug</t>
+          <t xml:space="preserve">Smith Machine Shoulder Press</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Traps</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbell Curl</t>
+          <t xml:space="preserve">Landmine Press</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biceps</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dumbbell Bicep Curl</t>
+          <t xml:space="preserve">Z Press</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biceps</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammer Curl</t>
+          <t xml:space="preserve">Behind-the-Neck Press</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biceps</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incline Dumbbell Curl</t>
+          <t xml:space="preserve">Lateral Raise</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biceps</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preacher Curl</t>
+          <t xml:space="preserve">Cable Lateral Raise</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biceps</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Curl</t>
+          <t xml:space="preserve">Machine Lateral Raise</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biceps</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back Squat</t>
+          <t xml:space="preserve">Leaning Lateral Raise</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quads</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Front Squat</t>
+          <t xml:space="preserve">Front Raise</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quads</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goblet Squat</t>
+          <t xml:space="preserve">Cable Front Raise</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quads</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hack Squat</t>
+          <t xml:space="preserve">Plate Front Raise</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quads</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leg Press</t>
+          <t xml:space="preserve">Upright Row</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quads</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulgarian Split Squat</t>
+          <t xml:space="preserve">Cable Upright Row</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quads</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walking Lunge</t>
+          <t xml:space="preserve">Close-Grip Bench Press</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quads</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step-Up</t>
+          <t xml:space="preserve">Triceps Rope Pushdown</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quads</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leg Extension</t>
+          <t xml:space="preserve">Triceps Cable Pushdown</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quads</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Romanian Deadlift</t>
+          <t xml:space="preserve">Straight-Bar Pushdown</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hamstrings</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stiff-Leg Deadlift</t>
+          <t xml:space="preserve">Reverse-Grip Pushdown</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hamstrings</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lying Leg Curl</t>
+          <t xml:space="preserve">Overhead Triceps Extension</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hamstrings</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seated Leg Curl</t>
+          <t xml:space="preserve">Cable Overhead Extension</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hamstrings</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Good Morning</t>
+          <t xml:space="preserve">Skull Crusher</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hamstrings</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hip Thrust</t>
+          <t xml:space="preserve">EZ-Bar Skull Crusher</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glutes</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glute Bridge</t>
+          <t xml:space="preserve">Dumbbell Skull Crusher</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glutes</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Kickback</t>
+          <t xml:space="preserve">JM Press</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glutes</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Standing Calf Raise</t>
+          <t xml:space="preserve">Tate Press</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calves</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seated Calf Raise</t>
+          <t xml:space="preserve">Triceps Kickback</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calves</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plank</t>
+          <t xml:space="preserve">Bench Dip</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanging Leg Raise</t>
+          <t xml:space="preserve">Machine Triceps Extension</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core</t>
+          <t xml:space="preserve">Push</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Crunch</t>
+          <t xml:space="preserve">Deadlift</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core</t>
+          <t xml:space="preserve">Back</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core</t>
+          <t xml:space="preserve">Pull</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ab Wheel Rollout</t>
+          <t xml:space="preserve">Sumo Deadlift</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core</t>
+          <t xml:space="preserve">Back</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core</t>
+          <t xml:space="preserve">Pull</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Russian Twist</t>
+          <t xml:space="preserve">Trap Bar Deadlift</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core</t>
+          <t xml:space="preserve">Back</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core</t>
+          <t xml:space="preserve">Pull</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Deficit Deadlift</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack Pull</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Barbell Row</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendlay Row</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yates Row</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dumbbell Row</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chest-Supported Row</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seal Row</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T-Bar Row</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Landmine Row</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meadows Row</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seated Cable Row</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wide-Grip Seated Row</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single-Arm Cable Row</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine Row</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inverted Row</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lat Pulldown</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wide-Grip Lat Pulldown</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Close-Grip Lat Pulldown</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reverse-Grip Lat Pulldown</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single-Arm Lat Pulldown</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Straight-Arm Pulldown</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull-Up</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weighted Pull-Up</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chin-Up</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weighted Chin-Up</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neutral-Grip Pull-Up</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assisted Pull-Up</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine Pullover</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dumbbell Pullover</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lats</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Face Pull</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear delts</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reverse Pec Deck</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear delts</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bent-Over Reverse Fly</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear delts</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable Reverse Fly</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear delts</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prone Y Raise</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear delts</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Band Pull-Apart</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rear delts</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Barbell Shrug</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traps</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dumbbell Shrug</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traps</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trap Bar Shrug</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traps</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable Shrug</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traps</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine Shrug</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traps</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Barbell Curl</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EZ-Bar Curl</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dumbbell Bicep Curl</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alternating Dumbbell Curl</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hammer Curl</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cross-Body Hammer Curl</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Incline Dumbbell Curl</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preacher Curl</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine Preacher Curl</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable Curl</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bayesian Cable Curl</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Concentration Curl</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spider Curl</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drag Curl</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reverse Curl</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biceps</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wrist Curl</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forearms</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reverse Wrist Curl</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forearms</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Behind-the-Back Wrist Curl</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forearms</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wrist Roller</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forearms</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plate Pinch</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forearms</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back Squat</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High-Bar Back Squat</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low-Bar Back Squat</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Front Squat</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Goblet Squat</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zercher Squat</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Box Squat</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pause Squat</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Safety Bar Squat</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Smith Machine Squat</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Belt Squat</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hack Squat</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine Hack Squat</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendulum Squat</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leg Press</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single-Leg Press</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulgarian Split Squat</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Split Squat</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Walking Lunge</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reverse Lunge</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forward Lunge</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lateral Lunge</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curtsy Lunge</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deficit Reverse Lunge</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step-Up</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leg Extension</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single-Leg Extension</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sissy Squat</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wall Sit</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quads</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Romanian Deadlift</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamstrings</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dumbbell Romanian Deadlift</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamstrings</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single-Leg Romanian Deadlift</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamstrings</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stiff-Leg Deadlift</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamstrings</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lying Leg Curl</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamstrings</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seated Leg Curl</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamstrings</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standing Leg Curl</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamstrings</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nordic Curl</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamstrings</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glute-Ham Raise</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamstrings</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Good Morning</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamstrings</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Back Extension</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamstrings</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45-Degree Back Extension</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamstrings</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hip Thrust</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glutes</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Barbell Hip Thrust</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glutes</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single-Leg Hip Thrust</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glutes</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine Hip Thrust</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glutes</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glute Bridge</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glutes</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable Kickback</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glutes</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine Glute Kickback</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glutes</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable Pull-Through</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glutes</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frog Pump</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Glutes</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adductor Machine</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adductors</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Copenhagen Plank</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adductors</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sumo Squat</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adductors</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cossack Squat</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adductors</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abductor Machine</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abductors</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable Hip Abduction</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abductors</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Banded Lateral Walk</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abductors</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clamshell</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abductors</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standing Calf Raise</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calves</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seated Calf Raise</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calves</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leg Press Calf Raise</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calves</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Smith Machine Calf Raise</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calves</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single-Leg Calf Raise</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calves</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Donkey Calf Raise</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calves</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tibialis Raise</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calves</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Legs</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plank</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Side Plank</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RKC Plank</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hollow Body Hold</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dead Bug</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bird Dog</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanging Leg Raise</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanging Knee Raise</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Captain's Chair Leg Raise</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lying Leg Raise</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toes-to-Bar</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dragon Flag</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">V-Up</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sit-Up</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decline Sit-Up</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crunch</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bicycle Crunch</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reverse Crunch</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cable Crunch</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ab Wheel Rollout</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Russian Twist</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pallof Press</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Landmine Twist</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Woodchopper</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mountain Climber</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
           <t xml:space="preserve">Farmer Carry</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Core</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Core</t>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suitcase Carry</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neck Curl</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neck</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neck Extension</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neck</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neck Harness Raise</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neck</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power Clean</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hang Clean</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clean and Jerk</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snatch</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Power Snatch</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hang Snatch</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clean Pull</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Snatch Pull</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Overhead Squat</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thruster</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kettlebell Swing</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kettlebell Clean</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kettlebell Snatch</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turkish Get-Up</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Burpee</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Man Maker</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sled Push</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sled Pull</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Battle Ropes</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Box Jump</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Broad Jump</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medicine Ball Slam</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medicine Ball Chest Pass</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full body</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rowing Machine</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assault Bike</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ski Erg</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Treadmill Run</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Incline Treadmill Walk</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stationary Bike</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stair Climber</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elliptical</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jump Rope</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint Interval</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditioning</t>
         </is>
       </c>
     </row>
@@ -1653,4 +4856,101 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what it does</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pr_rep_targets</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1,5,10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Track the heaviest weight lifted for a set of at least this many reps. Comma-separated, e.g. 1,3,5,8,10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pr_metrics</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">est1rm,volume,reps</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Extra records to track. Any of: est1rm (estimated one-rep max), volume (best single set), reps (most reps in a set), session (best total volume for one exercise in one session).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exercise</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Record</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Day</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/docs/download/training-tracker-template.xlsx
+++ b/docs/download/training-tracker-template.xlsx
@@ -89,6 +89,11 @@
           <t xml:space="preserve">image</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no weight</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -463,6 +468,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -480,6 +490,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -497,6 +512,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -514,6 +534,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -531,6 +556,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -548,6 +578,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -565,6 +600,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1160,6 +1200,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1500,6 +1545,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1619,6 +1669,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1653,6 +1708,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1687,6 +1747,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2741,6 +2806,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2758,6 +2828,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2894,6 +2969,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3149,6 +3229,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3183,6 +3268,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3234,6 +3324,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3251,6 +3346,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3387,6 +3487,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3404,6 +3509,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3421,6 +3531,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3438,6 +3553,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -3455,6 +3575,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3472,6 +3597,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -3489,6 +3619,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -3506,6 +3641,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -3523,6 +3663,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -3540,6 +3685,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -3557,6 +3707,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -3574,6 +3729,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -3591,6 +3751,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -3608,6 +3773,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -3625,6 +3795,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -3642,6 +3817,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -3659,6 +3839,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -3676,6 +3861,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -3795,6 +3985,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4135,6 +4330,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4203,6 +4403,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4220,6 +4425,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4237,6 +4447,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4288,6 +4503,11 @@
           <t xml:space="preserve">Conditioning</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4305,6 +4525,11 @@
           <t xml:space="preserve">Conditioning</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4322,6 +4547,11 @@
           <t xml:space="preserve">Conditioning</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -4339,6 +4569,11 @@
           <t xml:space="preserve">Conditioning</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -4356,6 +4591,11 @@
           <t xml:space="preserve">Conditioning</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -4373,6 +4613,11 @@
           <t xml:space="preserve">Conditioning</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -4390,6 +4635,11 @@
           <t xml:space="preserve">Conditioning</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -4407,6 +4657,11 @@
           <t xml:space="preserve">Conditioning</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -4424,6 +4679,11 @@
           <t xml:space="preserve">Conditioning</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -4439,6 +4699,11 @@
       <c r="C257" t="inlineStr">
         <is>
           <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
@@ -4475,6 +4740,11 @@
           <t xml:space="preserve">weight</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">default</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/docs/download/training-tracker-template.xlsx
+++ b/docs/download/training-tracker-template.xlsx
@@ -4829,6 +4829,11 @@
       <c r="E5">
         <v>0</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4997,6 +5002,11 @@
       <c r="E13">
         <v>0</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5122,6 +5132,11 @@
       </c>
       <c r="E19">
         <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/download/training-tracker-template.xlsx
+++ b/docs/download/training-tracker-template.xlsx
@@ -4742,7 +4742,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">default</t>
+          <t xml:space="preserve">include in new session</t>
         </is>
       </c>
     </row>

--- a/docs/download/training-tracker-template.xlsx
+++ b/docs/download/training-tracker-template.xlsx
@@ -94,6 +94,11 @@
           <t xml:space="preserve">no weight</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">video</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -128,6 +133,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Bench+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -145,6 +155,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Barbell+Bench+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -162,6 +177,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Decline+Barbell+Bench+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -179,6 +199,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Bench+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -196,6 +221,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Dumbbell+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -213,6 +243,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Decline+Dumbbell+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -230,6 +265,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Chest+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -247,6 +287,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Machine+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -264,6 +309,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Smith+Machine+Bench+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -281,6 +331,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Floor+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -298,6 +353,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pin+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -315,6 +375,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Board+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -332,6 +397,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Spoto+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -349,6 +419,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Chest+Fly+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -366,6 +441,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Low-to-High+Cable+Fly+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -383,6 +463,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=High-to-Low+Cable+Fly+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -400,6 +485,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Fly+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -417,6 +507,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Dumbbell+Fly+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -434,6 +529,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pec+Deck+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -451,6 +551,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Svend+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -473,6 +578,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Push-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -495,6 +605,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Push-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -517,6 +632,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Decline+Push-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -539,6 +659,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Diamond+Push-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -561,6 +686,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Deficit+Push-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -583,6 +713,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Chest+Dip+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -605,6 +740,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Ring+Dip+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -622,6 +762,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Overhead+Barbell+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -639,6 +784,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Barbell+Shoulder+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -656,6 +806,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Push+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -673,6 +828,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Push+Jerk+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -690,6 +850,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Dumbbell+Shoulder+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -707,6 +872,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Standing+Dumbbell+Shoulder+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -724,6 +894,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Arnold+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -741,6 +916,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Shoulder+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -758,6 +938,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Smith+Machine+Shoulder+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -775,6 +960,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Landmine+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -792,6 +982,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Z+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -809,6 +1004,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Behind-the-Neck+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -826,6 +1026,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lateral+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -843,6 +1048,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Lateral+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -860,6 +1070,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Lateral+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -877,6 +1092,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Leaning+Lateral+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -894,6 +1114,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Front+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -911,6 +1136,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Front+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -928,6 +1158,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Plate+Front+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -945,6 +1180,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Upright+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -962,6 +1202,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Upright+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -979,6 +1224,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Close-Grip+Bench+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -996,6 +1246,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Triceps+Rope+Pushdown+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1013,6 +1268,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Triceps+Cable+Pushdown+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1030,6 +1290,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Straight-Bar+Pushdown+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1047,6 +1312,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse-Grip+Pushdown+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1064,6 +1334,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Overhead+Triceps+Extension+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1081,6 +1356,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Overhead+Extension+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1098,6 +1378,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Skull+Crusher+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1115,6 +1400,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=EZ-Bar+Skull+Crusher+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1132,6 +1422,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Skull+Crusher+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1149,6 +1444,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=JM+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1166,6 +1466,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Tate+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1183,6 +1488,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Triceps+Kickback+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1205,6 +1515,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bench+Dip+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1222,6 +1537,11 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Triceps+Extension+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1239,6 +1559,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Deadlift+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1256,6 +1581,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sumo+Deadlift+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1273,6 +1603,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Trap+Bar+Deadlift+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1290,6 +1625,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Deficit+Deadlift+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1307,6 +1647,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Rack+Pull+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1324,6 +1669,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1341,6 +1691,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pendlay+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1358,6 +1713,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Yates+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1375,6 +1735,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1392,6 +1757,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Chest-Supported+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1409,6 +1779,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seal+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1426,6 +1801,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=T-Bar+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1443,6 +1823,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Landmine+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1460,6 +1845,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Meadows+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1477,6 +1867,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Cable+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1494,6 +1889,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wide-Grip+Seated+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1511,6 +1911,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Arm+Cable+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1528,6 +1933,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1550,6 +1960,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Inverted+Row+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1567,6 +1982,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lat+Pulldown+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1584,6 +2004,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wide-Grip+Lat+Pulldown+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1601,6 +2026,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Close-Grip+Lat+Pulldown+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1618,6 +2048,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse-Grip+Lat+Pulldown+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1635,6 +2070,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Arm+Lat+Pulldown+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1652,6 +2092,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Straight-Arm+Pulldown+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1674,6 +2119,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pull-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1691,6 +2141,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Weighted+Pull-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1713,6 +2168,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Chin-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1730,6 +2190,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Weighted+Chin-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1752,6 +2217,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Neutral-Grip+Pull-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1769,6 +2239,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Assisted+Pull-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1786,6 +2261,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Pullover+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1803,6 +2283,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Pullover+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1820,6 +2305,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Face+Pull+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1837,6 +2327,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Pec+Deck+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1854,6 +2349,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bent-Over+Reverse+Fly+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1871,6 +2371,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Reverse+Fly+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1888,6 +2393,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Prone+Y+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1905,6 +2415,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Band+Pull-Apart+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1922,6 +2437,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Shrug+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1939,6 +2459,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Shrug+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1956,6 +2481,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Trap+Bar+Shrug+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1973,6 +2503,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Shrug+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1990,6 +2525,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Shrug+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2007,6 +2547,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2024,6 +2569,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=EZ-Bar+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2041,6 +2591,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Bicep+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2058,6 +2613,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Alternating+Dumbbell+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2075,6 +2635,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hammer+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2092,6 +2657,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cross-Body+Hammer+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2109,6 +2679,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Dumbbell+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2126,6 +2701,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Preacher+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2143,6 +2723,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Preacher+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2160,6 +2745,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2177,6 +2767,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bayesian+Cable+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2194,6 +2789,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Concentration+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2211,6 +2811,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Spider+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2228,6 +2833,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Drag+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2245,6 +2855,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2262,6 +2877,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wrist+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2279,6 +2899,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Wrist+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2296,6 +2921,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Behind-the-Back+Wrist+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2313,6 +2943,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wrist+Roller+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2330,6 +2965,11 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Plate+Pinch+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2347,6 +2987,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Back+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2364,6 +3009,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=High-Bar+Back+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2381,6 +3031,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Low-Bar+Back+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2398,6 +3053,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Front+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2415,6 +3075,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Goblet+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2432,6 +3097,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Zercher+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2449,6 +3119,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Box+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2466,6 +3141,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pause+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2483,6 +3163,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Safety+Bar+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2500,6 +3185,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Smith+Machine+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2517,6 +3207,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Belt+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2534,6 +3229,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hack+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2551,6 +3251,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Hack+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2568,6 +3273,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pendulum+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2585,6 +3295,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Leg+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2602,6 +3317,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2619,6 +3339,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bulgarian+Split+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2636,6 +3361,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Split+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2653,6 +3383,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Walking+Lunge+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2670,6 +3405,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Lunge+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2687,6 +3427,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Forward+Lunge+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2704,6 +3449,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lateral+Lunge+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2721,6 +3471,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Curtsy+Lunge+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2738,6 +3493,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Deficit+Reverse+Lunge+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2755,6 +3515,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Step-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2772,6 +3537,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Leg+Extension+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2789,6 +3559,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Extension+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2811,6 +3586,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sissy+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2833,6 +3613,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wall+Sit+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2850,6 +3635,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Romanian+Deadlift+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2867,6 +3657,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Romanian+Deadlift+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2884,6 +3679,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Romanian+Deadlift+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2901,6 +3701,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Stiff-Leg+Deadlift+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2918,6 +3723,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lying+Leg+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2935,6 +3745,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Leg+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2952,6 +3767,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Standing+Leg+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2974,6 +3794,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Nordic+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2991,6 +3816,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Glute-Ham+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3008,6 +3838,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Good+Morning+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3025,6 +3860,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Back+Extension+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3042,6 +3882,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=45-Degree+Back+Extension+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3059,6 +3904,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hip+Thrust+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3076,6 +3926,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Hip+Thrust+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3093,6 +3948,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Hip+Thrust+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3110,6 +3970,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Hip+Thrust+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3127,6 +3992,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Glute+Bridge+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3144,6 +4014,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Kickback+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3161,6 +4036,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Glute+Kickback+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3178,6 +4058,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Pull-Through+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3195,6 +4080,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Frog+Pump+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3212,6 +4102,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Adductor+Machine+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3234,6 +4129,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Copenhagen+Plank+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3251,6 +4151,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sumo+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3273,6 +4178,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cossack+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3290,6 +4200,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Abductor+Machine+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3307,6 +4222,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Hip+Abduction+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3329,6 +4249,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Banded+Lateral+Walk+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3351,6 +4276,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Clamshell+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3368,6 +4298,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Standing+Calf+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3385,6 +4320,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Calf+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -3402,6 +4342,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Leg+Press+Calf+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3419,6 +4364,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Smith+Machine+Calf+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3436,6 +4386,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Calf+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3453,6 +4408,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Donkey+Calf+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3470,6 +4430,11 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Tibialis+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -3492,6 +4457,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Plank+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3514,6 +4484,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Side+Plank+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3536,6 +4511,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=RKC+Plank+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3558,6 +4538,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hollow+Body+Hold+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -3580,6 +4565,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dead+Bug+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3602,6 +4592,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bird+Dog+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -3624,6 +4619,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hanging+Leg+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -3646,6 +4646,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hanging+Knee+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -3668,6 +4673,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Captain%27s+Chair+Leg+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -3690,6 +4700,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lying+Leg+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -3712,6 +4727,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Toes-to-Bar+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -3734,6 +4754,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dragon+Flag+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -3756,6 +4781,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=V-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -3778,6 +4808,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sit-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -3800,6 +4835,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Decline+Sit-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -3822,6 +4862,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Crunch+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -3844,6 +4889,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bicycle+Crunch+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -3866,6 +4916,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Crunch+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -3883,6 +4938,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Crunch+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -3900,6 +4960,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Ab+Wheel+Rollout+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -3917,6 +4982,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Russian+Twist+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -3934,6 +5004,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pallof+Press+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -3951,6 +5026,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Landmine+Twist+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -3968,6 +5048,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Woodchopper+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -3990,6 +5075,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Mountain+Climber+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4007,6 +5097,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Farmer+Carry+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4024,6 +5119,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Suitcase+Carry+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4041,6 +5141,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Neck+Curl+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4058,6 +5163,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Neck+Extension+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4075,6 +5185,11 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Neck+Harness+Raise+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4092,6 +5207,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Power+Clean+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4109,6 +5229,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hang+Clean+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4126,6 +5251,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Clean+and+Jerk+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4143,6 +5273,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Snatch+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4160,6 +5295,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Power+Snatch+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4177,6 +5317,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hang+Snatch+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4194,6 +5339,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Clean+Pull+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4211,6 +5361,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Snatch+Pull+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4228,6 +5383,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Overhead+Squat+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4245,6 +5405,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Thruster+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4262,6 +5427,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Kettlebell+Swing+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4279,6 +5449,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Kettlebell+Clean+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4296,6 +5471,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Kettlebell+Snatch+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4313,6 +5493,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Turkish+Get-Up+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4335,6 +5520,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Burpee+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4352,6 +5542,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Man+Maker+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4369,6 +5564,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sled+Push+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4386,6 +5586,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sled+Pull+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4408,6 +5613,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Battle+Ropes+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4430,6 +5640,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Box+Jump+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4452,6 +5667,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Broad+Jump+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4469,6 +5689,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Medicine+Ball+Slam+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4486,6 +5711,11 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Medicine+Ball+Chest+Pass+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4508,6 +5738,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Rowing+Machine+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4530,6 +5765,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Assault+Bike+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4552,6 +5792,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Ski+Erg+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -4574,6 +5819,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Treadmill+Run+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -4596,6 +5846,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Treadmill+Walk+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -4618,6 +5873,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Stationary+Bike+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -4640,6 +5900,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Stair+Climber+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -4662,6 +5927,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Elliptical+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -4684,6 +5954,11 @@
           <t xml:space="preserve">yes</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Jump+Rope+proper+form</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -4704,6 +5979,11 @@
       <c r="E257" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sprint+Interval+proper+form</t>
         </is>
       </c>
     </row>

--- a/docs/download/training-tracker-template.xlsx
+++ b/docs/download/training-tracker-template.xlsx
@@ -37,7 +37,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reps</t>
+          <t xml:space="preserve">Reps / Secs</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -99,6 +99,11 @@
           <t xml:space="preserve">video</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">time based</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2970,6 +2975,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Plate+Pinch+proper+form</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3618,6 +3628,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Wall+Sit+proper+form</t>
         </is>
       </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4134,6 +4149,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Copenhagen+Plank+proper+form</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4462,6 +4482,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Plank+proper+form</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4489,6 +4514,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Side+Plank+proper+form</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4516,6 +4546,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=RKC+Plank+proper+form</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4543,6 +4578,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Hollow+Body+Hold+proper+form</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5080,6 +5120,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Mountain+Climber+proper+form</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5102,6 +5147,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Farmer+Carry+proper+form</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5124,6 +5174,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Suitcase+Carry+proper+form</t>
         </is>
       </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5569,6 +5624,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Sled+Push+proper+form</t>
         </is>
       </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5591,6 +5651,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Sled+Pull+proper+form</t>
         </is>
       </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5618,6 +5683,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Battle+Ropes+proper+form</t>
         </is>
       </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5743,6 +5813,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Rowing+Machine+proper+form</t>
         </is>
       </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5770,6 +5845,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Assault+Bike+proper+form</t>
         </is>
       </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5797,6 +5877,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Ski+Erg+proper+form</t>
         </is>
       </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5824,6 +5909,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Treadmill+Run+proper+form</t>
         </is>
       </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5851,6 +5941,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Treadmill+Walk+proper+form</t>
         </is>
       </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5878,6 +5973,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Stationary+Bike+proper+form</t>
         </is>
       </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5905,6 +6005,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Stair+Climber+proper+form</t>
         </is>
       </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5932,6 +6037,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Elliptical+proper+form</t>
         </is>
       </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5959,6 +6069,11 @@
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Jump+Rope+proper+form</t>
         </is>
       </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5984,6 +6099,11 @@
       <c r="F257" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.youtube.com/results?search_query=Sprint+Interval+proper+form</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>

--- a/docs/download/training-tracker-template.xlsx
+++ b/docs/download/training-tracker-template.xlsx
@@ -108,24 +108,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Other]</t>
+          <t xml:space="preserve">Barbell Bench Press</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placeholder</t>
+          <t xml:space="preserve">Chest</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Any</t>
+          <t xml:space="preserve">Push</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Bench+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbell Bench Press</t>
+          <t xml:space="preserve">Incline Barbell Bench Press</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -140,14 +145,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Bench+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Barbell+Bench+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incline Barbell Bench Press</t>
+          <t xml:space="preserve">Decline Barbell Bench Press</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -162,14 +167,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Barbell+Bench+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Decline+Barbell+Bench+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decline Barbell Bench Press</t>
+          <t xml:space="preserve">Dumbbell Bench Press</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -184,14 +189,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Decline+Barbell+Bench+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Bench+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dumbbell Bench Press</t>
+          <t xml:space="preserve">Incline Dumbbell Press</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -206,14 +211,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Bench+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Dumbbell+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incline Dumbbell Press</t>
+          <t xml:space="preserve">Decline Dumbbell Press</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -228,14 +233,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Dumbbell+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Decline+Dumbbell+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decline Dumbbell Press</t>
+          <t xml:space="preserve">Machine Chest Press</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -250,14 +255,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Decline+Dumbbell+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Chest+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine Chest Press</t>
+          <t xml:space="preserve">Incline Machine Press</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -272,14 +277,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Chest+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Machine+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incline Machine Press</t>
+          <t xml:space="preserve">Smith Machine Bench Press</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -294,14 +299,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Machine+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Smith+Machine+Bench+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smith Machine Bench Press</t>
+          <t xml:space="preserve">Floor Press</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -316,14 +321,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Smith+Machine+Bench+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Floor+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Floor Press</t>
+          <t xml:space="preserve">Pin Press</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -338,14 +343,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Floor+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pin+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pin Press</t>
+          <t xml:space="preserve">Board Press</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -360,14 +365,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pin+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Board+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Board Press</t>
+          <t xml:space="preserve">Spoto Press</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -382,14 +387,14 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Board+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Spoto+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spoto Press</t>
+          <t xml:space="preserve">Cable Chest Fly</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -404,14 +409,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Spoto+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Chest+Fly+proper+form</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Chest Fly</t>
+          <t xml:space="preserve">Low-to-High Cable Fly</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -426,14 +431,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Chest+Fly+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Low-to-High+Cable+Fly+proper+form</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low-to-High Cable Fly</t>
+          <t xml:space="preserve">High-to-Low Cable Fly</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -448,14 +453,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Low-to-High+Cable+Fly+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=High-to-Low+Cable+Fly+proper+form</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">High-to-Low Cable Fly</t>
+          <t xml:space="preserve">Dumbbell Fly</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -470,14 +475,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=High-to-Low+Cable+Fly+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Fly+proper+form</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dumbbell Fly</t>
+          <t xml:space="preserve">Incline Dumbbell Fly</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -492,14 +497,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Fly+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Dumbbell+Fly+proper+form</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incline Dumbbell Fly</t>
+          <t xml:space="preserve">Pec Deck</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -514,14 +519,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Dumbbell+Fly+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pec+Deck+proper+form</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pec Deck</t>
+          <t xml:space="preserve">Svend Press</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -536,14 +541,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pec+Deck+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Svend+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svend Press</t>
+          <t xml:space="preserve">Push-Up</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -556,16 +561,21 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Svend+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Push-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Push-Up</t>
+          <t xml:space="preserve">Incline Push-Up</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -585,14 +595,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Push-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Push-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incline Push-Up</t>
+          <t xml:space="preserve">Decline Push-Up</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -612,14 +622,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Push-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Decline+Push-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decline Push-Up</t>
+          <t xml:space="preserve">Diamond Push-Up</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -639,14 +649,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Decline+Push-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Diamond+Push-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diamond Push-Up</t>
+          <t xml:space="preserve">Deficit Push-Up</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -666,14 +676,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Diamond+Push-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Deficit+Push-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deficit Push-Up</t>
+          <t xml:space="preserve">Chest Dip</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -693,14 +703,14 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Deficit+Push-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Chest+Dip+proper+form</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chest Dip</t>
+          <t xml:space="preserve">Ring Dip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -720,19 +730,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Chest+Dip+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Ring+Dip+proper+form</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ring Dip</t>
+          <t xml:space="preserve">Overhead Barbell Press</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chest</t>
+          <t xml:space="preserve">Shoulders</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -740,21 +750,16 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Ring+Dip+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Overhead+Barbell+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overhead Barbell Press</t>
+          <t xml:space="preserve">Seated Barbell Shoulder Press</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -769,14 +774,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Overhead+Barbell+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Barbell+Shoulder+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seated Barbell Shoulder Press</t>
+          <t xml:space="preserve">Push Press</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -791,14 +796,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Barbell+Shoulder+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Push+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Push Press</t>
+          <t xml:space="preserve">Push Jerk</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -813,14 +818,14 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Push+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Push+Jerk+proper+form</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Push Jerk</t>
+          <t xml:space="preserve">Seated Dumbbell Shoulder Press</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -835,14 +840,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Push+Jerk+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Dumbbell+Shoulder+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seated Dumbbell Shoulder Press</t>
+          <t xml:space="preserve">Standing Dumbbell Shoulder Press</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -857,14 +862,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Dumbbell+Shoulder+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Standing+Dumbbell+Shoulder+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Standing Dumbbell Shoulder Press</t>
+          <t xml:space="preserve">Arnold Press</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -879,14 +884,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Standing+Dumbbell+Shoulder+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Arnold+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arnold Press</t>
+          <t xml:space="preserve">Machine Shoulder Press</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -901,14 +906,14 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Arnold+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Shoulder+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine Shoulder Press</t>
+          <t xml:space="preserve">Smith Machine Shoulder Press</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -923,14 +928,14 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Shoulder+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Smith+Machine+Shoulder+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smith Machine Shoulder Press</t>
+          <t xml:space="preserve">Landmine Press</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -945,14 +950,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Smith+Machine+Shoulder+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Landmine+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landmine Press</t>
+          <t xml:space="preserve">Z Press</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -967,14 +972,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Landmine+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Z+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z Press</t>
+          <t xml:space="preserve">Behind-the-Neck Press</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -989,14 +994,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Z+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Behind-the-Neck+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Behind-the-Neck Press</t>
+          <t xml:space="preserve">Lateral Raise</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1011,14 +1016,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Behind-the-Neck+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lateral+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lateral Raise</t>
+          <t xml:space="preserve">Cable Lateral Raise</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1033,14 +1038,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lateral+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Lateral+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Lateral Raise</t>
+          <t xml:space="preserve">Machine Lateral Raise</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1055,14 +1060,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Lateral+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Lateral+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine Lateral Raise</t>
+          <t xml:space="preserve">Leaning Lateral Raise</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1077,14 +1082,14 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Lateral+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Leaning+Lateral+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leaning Lateral Raise</t>
+          <t xml:space="preserve">Front Raise</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1099,14 +1104,14 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Leaning+Lateral+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Front+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Front Raise</t>
+          <t xml:space="preserve">Cable Front Raise</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1121,14 +1126,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Front+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Front+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Front Raise</t>
+          <t xml:space="preserve">Plate Front Raise</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1143,14 +1148,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Front+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Plate+Front+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate Front Raise</t>
+          <t xml:space="preserve">Upright Row</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1165,14 +1170,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Plate+Front+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Upright+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upright Row</t>
+          <t xml:space="preserve">Cable Upright Row</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1187,19 +1192,19 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Upright+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Upright+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Upright Row</t>
+          <t xml:space="preserve">Close-Grip Bench Press</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shoulders</t>
+          <t xml:space="preserve">Triceps</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1209,14 +1214,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Upright+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Close-Grip+Bench+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Close-Grip Bench Press</t>
+          <t xml:space="preserve">Triceps Rope Pushdown</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1231,14 +1236,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Close-Grip+Bench+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Triceps+Rope+Pushdown+proper+form</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triceps Rope Pushdown</t>
+          <t xml:space="preserve">Triceps Cable Pushdown</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1253,14 +1258,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Triceps+Rope+Pushdown+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Triceps+Cable+Pushdown+proper+form</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triceps Cable Pushdown</t>
+          <t xml:space="preserve">Straight-Bar Pushdown</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1275,14 +1280,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Triceps+Cable+Pushdown+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Straight-Bar+Pushdown+proper+form</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Straight-Bar Pushdown</t>
+          <t xml:space="preserve">Reverse-Grip Pushdown</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1297,14 +1302,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Straight-Bar+Pushdown+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse-Grip+Pushdown+proper+form</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reverse-Grip Pushdown</t>
+          <t xml:space="preserve">Overhead Triceps Extension</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1319,14 +1324,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse-Grip+Pushdown+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Overhead+Triceps+Extension+proper+form</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overhead Triceps Extension</t>
+          <t xml:space="preserve">Cable Overhead Extension</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1341,14 +1346,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Overhead+Triceps+Extension+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Overhead+Extension+proper+form</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Overhead Extension</t>
+          <t xml:space="preserve">Skull Crusher</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1363,14 +1368,14 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Overhead+Extension+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Skull+Crusher+proper+form</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skull Crusher</t>
+          <t xml:space="preserve">EZ-Bar Skull Crusher</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1385,14 +1390,14 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Skull+Crusher+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=EZ-Bar+Skull+Crusher+proper+form</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">EZ-Bar Skull Crusher</t>
+          <t xml:space="preserve">Dumbbell Skull Crusher</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1407,14 +1412,14 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=EZ-Bar+Skull+Crusher+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Skull+Crusher+proper+form</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dumbbell Skull Crusher</t>
+          <t xml:space="preserve">JM Press</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1429,14 +1434,14 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Skull+Crusher+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=JM+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">JM Press</t>
+          <t xml:space="preserve">Tate Press</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1451,14 +1456,14 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=JM+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Tate+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tate Press</t>
+          <t xml:space="preserve">Triceps Kickback</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1473,14 +1478,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Tate+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Triceps+Kickback+proper+form</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triceps Kickback</t>
+          <t xml:space="preserve">Bench Dip</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1493,16 +1498,21 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Triceps+Kickback+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bench+Dip+proper+form</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bench Dip</t>
+          <t xml:space="preserve">Machine Triceps Extension</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1515,43 +1525,38 @@
           <t xml:space="preserve">Push</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bench+Dip+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Triceps+Extension+proper+form</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine Triceps Extension</t>
+          <t xml:space="preserve">Deadlift</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triceps</t>
+          <t xml:space="preserve">Back</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Push</t>
+          <t xml:space="preserve">Pull</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Triceps+Extension+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Deadlift+proper+form</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deadlift</t>
+          <t xml:space="preserve">Sumo Deadlift</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1566,14 +1571,14 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Deadlift+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sumo+Deadlift+proper+form</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sumo Deadlift</t>
+          <t xml:space="preserve">Trap Bar Deadlift</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1588,14 +1593,14 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sumo+Deadlift+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Trap+Bar+Deadlift+proper+form</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trap Bar Deadlift</t>
+          <t xml:space="preserve">Deficit Deadlift</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1610,14 +1615,14 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Trap+Bar+Deadlift+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Deficit+Deadlift+proper+form</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deficit Deadlift</t>
+          <t xml:space="preserve">Rack Pull</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1632,14 +1637,14 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Deficit+Deadlift+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Rack+Pull+proper+form</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rack Pull</t>
+          <t xml:space="preserve">Barbell Row</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1654,14 +1659,14 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Rack+Pull+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbell Row</t>
+          <t xml:space="preserve">Pendlay Row</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1676,14 +1681,14 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pendlay+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pendlay Row</t>
+          <t xml:space="preserve">Yates Row</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1698,14 +1703,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pendlay+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Yates+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yates Row</t>
+          <t xml:space="preserve">Dumbbell Row</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1720,14 +1725,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Yates+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dumbbell Row</t>
+          <t xml:space="preserve">Chest-Supported Row</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1742,14 +1747,14 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Chest-Supported+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chest-Supported Row</t>
+          <t xml:space="preserve">Seal Row</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1764,14 +1769,14 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Chest-Supported+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seal+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal Row</t>
+          <t xml:space="preserve">T-Bar Row</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1786,14 +1791,14 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seal+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=T-Bar+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">T-Bar Row</t>
+          <t xml:space="preserve">Landmine Row</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1808,14 +1813,14 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=T-Bar+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Landmine+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landmine Row</t>
+          <t xml:space="preserve">Meadows Row</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1830,14 +1835,14 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Landmine+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Meadows+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meadows Row</t>
+          <t xml:space="preserve">Seated Cable Row</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1852,14 +1857,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Meadows+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Cable+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seated Cable Row</t>
+          <t xml:space="preserve">Wide-Grip Seated Row</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1874,14 +1879,14 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Cable+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wide-Grip+Seated+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wide-Grip Seated Row</t>
+          <t xml:space="preserve">Single-Arm Cable Row</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1896,14 +1901,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wide-Grip+Seated+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Arm+Cable+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single-Arm Cable Row</t>
+          <t xml:space="preserve">Machine Row</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1918,14 +1923,14 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Arm+Cable+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine Row</t>
+          <t xml:space="preserve">Inverted Row</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1938,21 +1943,26 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Inverted+Row+proper+form</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inverted Row</t>
+          <t xml:space="preserve">Lat Pulldown</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back</t>
+          <t xml:space="preserve">Lats</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1960,21 +1970,16 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Inverted+Row+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lat+Pulldown+proper+form</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lat Pulldown</t>
+          <t xml:space="preserve">Wide-Grip Lat Pulldown</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1989,14 +1994,14 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lat+Pulldown+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wide-Grip+Lat+Pulldown+proper+form</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wide-Grip Lat Pulldown</t>
+          <t xml:space="preserve">Close-Grip Lat Pulldown</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2011,14 +2016,14 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wide-Grip+Lat+Pulldown+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Close-Grip+Lat+Pulldown+proper+form</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Close-Grip Lat Pulldown</t>
+          <t xml:space="preserve">Reverse-Grip Lat Pulldown</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2033,14 +2038,14 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Close-Grip+Lat+Pulldown+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse-Grip+Lat+Pulldown+proper+form</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reverse-Grip Lat Pulldown</t>
+          <t xml:space="preserve">Single-Arm Lat Pulldown</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2055,14 +2060,14 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse-Grip+Lat+Pulldown+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Arm+Lat+Pulldown+proper+form</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single-Arm Lat Pulldown</t>
+          <t xml:space="preserve">Straight-Arm Pulldown</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2077,14 +2082,14 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Arm+Lat+Pulldown+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Straight-Arm+Pulldown+proper+form</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Straight-Arm Pulldown</t>
+          <t xml:space="preserve">Pull-Up</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2097,16 +2102,21 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Straight-Arm+Pulldown+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pull-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull-Up</t>
+          <t xml:space="preserve">Weighted Pull-Up</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2119,21 +2129,16 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pull-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Weighted+Pull-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weighted Pull-Up</t>
+          <t xml:space="preserve">Chin-Up</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2146,16 +2151,21 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Weighted+Pull-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Chin-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chin-Up</t>
+          <t xml:space="preserve">Weighted Chin-Up</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2168,21 +2178,16 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Chin-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Weighted+Chin-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weighted Chin-Up</t>
+          <t xml:space="preserve">Neutral-Grip Pull-Up</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2195,16 +2200,21 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Weighted+Chin-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Neutral-Grip+Pull-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neutral-Grip Pull-Up</t>
+          <t xml:space="preserve">Assisted Pull-Up</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2217,21 +2227,16 @@
           <t xml:space="preserve">Pull</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Neutral-Grip+Pull-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Assisted+Pull-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assisted Pull-Up</t>
+          <t xml:space="preserve">Machine Pullover</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2246,14 +2251,14 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Assisted+Pull-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Pullover+proper+form</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine Pullover</t>
+          <t xml:space="preserve">Dumbbell Pullover</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2268,19 +2273,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Pullover+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Pullover+proper+form</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dumbbell Pullover</t>
+          <t xml:space="preserve">Face Pull</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lats</t>
+          <t xml:space="preserve">Rear delts</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2290,14 +2295,14 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Pullover+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Face+Pull+proper+form</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Face Pull</t>
+          <t xml:space="preserve">Reverse Pec Deck</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2312,14 +2317,14 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Face+Pull+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Pec+Deck+proper+form</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reverse Pec Deck</t>
+          <t xml:space="preserve">Bent-Over Reverse Fly</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2334,14 +2339,14 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Pec+Deck+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bent-Over+Reverse+Fly+proper+form</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bent-Over Reverse Fly</t>
+          <t xml:space="preserve">Cable Reverse Fly</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2356,14 +2361,14 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bent-Over+Reverse+Fly+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Reverse+Fly+proper+form</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Reverse Fly</t>
+          <t xml:space="preserve">Prone Y Raise</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2378,14 +2383,14 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Reverse+Fly+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Prone+Y+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prone Y Raise</t>
+          <t xml:space="preserve">Band Pull-Apart</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2400,19 +2405,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Prone+Y+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Band+Pull-Apart+proper+form</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Band Pull-Apart</t>
+          <t xml:space="preserve">Barbell Shrug</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rear delts</t>
+          <t xml:space="preserve">Traps</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2422,14 +2427,14 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Band+Pull-Apart+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Shrug+proper+form</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbell Shrug</t>
+          <t xml:space="preserve">Dumbbell Shrug</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2444,14 +2449,14 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Shrug+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Shrug+proper+form</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dumbbell Shrug</t>
+          <t xml:space="preserve">Trap Bar Shrug</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2466,14 +2471,14 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Shrug+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Trap+Bar+Shrug+proper+form</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trap Bar Shrug</t>
+          <t xml:space="preserve">Cable Shrug</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2488,14 +2493,14 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Trap+Bar+Shrug+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Shrug+proper+form</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Shrug</t>
+          <t xml:space="preserve">Machine Shrug</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2510,19 +2515,19 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Shrug+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Shrug+proper+form</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine Shrug</t>
+          <t xml:space="preserve">Barbell Curl</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Traps</t>
+          <t xml:space="preserve">Biceps</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2532,14 +2537,14 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Shrug+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbell Curl</t>
+          <t xml:space="preserve">EZ-Bar Curl</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2554,14 +2559,14 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=EZ-Bar+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">EZ-Bar Curl</t>
+          <t xml:space="preserve">Dumbbell Bicep Curl</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2576,14 +2581,14 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=EZ-Bar+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Bicep+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dumbbell Bicep Curl</t>
+          <t xml:space="preserve">Alternating Dumbbell Curl</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2598,14 +2603,14 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Bicep+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Alternating+Dumbbell+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alternating Dumbbell Curl</t>
+          <t xml:space="preserve">Hammer Curl</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2620,14 +2625,14 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Alternating+Dumbbell+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hammer+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammer Curl</t>
+          <t xml:space="preserve">Cross-Body Hammer Curl</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2642,14 +2647,14 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hammer+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cross-Body+Hammer+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cross-Body Hammer Curl</t>
+          <t xml:space="preserve">Incline Dumbbell Curl</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2664,14 +2669,14 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cross-Body+Hammer+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Dumbbell+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incline Dumbbell Curl</t>
+          <t xml:space="preserve">Preacher Curl</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2686,14 +2691,14 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Dumbbell+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Preacher+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preacher Curl</t>
+          <t xml:space="preserve">Machine Preacher Curl</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2708,14 +2713,14 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Preacher+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Preacher+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine Preacher Curl</t>
+          <t xml:space="preserve">Cable Curl</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2730,14 +2735,14 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Preacher+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Curl</t>
+          <t xml:space="preserve">Bayesian Cable Curl</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2752,14 +2757,14 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bayesian+Cable+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bayesian Cable Curl</t>
+          <t xml:space="preserve">Concentration Curl</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2774,14 +2779,14 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bayesian+Cable+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Concentration+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concentration Curl</t>
+          <t xml:space="preserve">Spider Curl</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2796,14 +2801,14 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Concentration+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Spider+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spider Curl</t>
+          <t xml:space="preserve">Drag Curl</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2818,14 +2823,14 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Spider+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Drag+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drag Curl</t>
+          <t xml:space="preserve">Reverse Curl</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2840,19 +2845,19 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Drag+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reverse Curl</t>
+          <t xml:space="preserve">Wrist Curl</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biceps</t>
+          <t xml:space="preserve">Forearms</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2862,14 +2867,14 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wrist+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wrist Curl</t>
+          <t xml:space="preserve">Reverse Wrist Curl</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2884,14 +2889,14 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wrist+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Wrist+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reverse Wrist Curl</t>
+          <t xml:space="preserve">Behind-the-Back Wrist Curl</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2906,14 +2911,14 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Wrist+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Behind-the-Back+Wrist+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Behind-the-Back Wrist Curl</t>
+          <t xml:space="preserve">Wrist Roller</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2928,14 +2933,14 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Behind-the-Back+Wrist+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wrist+Roller+proper+form</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wrist Roller</t>
+          <t xml:space="preserve">Plate Pinch</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2950,41 +2955,41 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wrist+Roller+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Plate+Pinch+proper+form</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plate Pinch</t>
+          <t xml:space="preserve">Back Squat</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forearms</t>
+          <t xml:space="preserve">Quads</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pull</t>
+          <t xml:space="preserve">Legs</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Plate+Pinch+proper+form</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Back+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back Squat</t>
+          <t xml:space="preserve">High-Bar Back Squat</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2999,14 +3004,14 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Back+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=High-Bar+Back+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">High-Bar Back Squat</t>
+          <t xml:space="preserve">Low-Bar Back Squat</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3021,14 +3026,14 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=High-Bar+Back+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Low-Bar+Back+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low-Bar Back Squat</t>
+          <t xml:space="preserve">Front Squat</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3043,14 +3048,14 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Low-Bar+Back+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Front+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Front Squat</t>
+          <t xml:space="preserve">Goblet Squat</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3065,14 +3070,14 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Front+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Goblet+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goblet Squat</t>
+          <t xml:space="preserve">Zercher Squat</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3087,14 +3092,14 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Goblet+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Zercher+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zercher Squat</t>
+          <t xml:space="preserve">Box Squat</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3109,14 +3114,14 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Zercher+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Box+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Squat</t>
+          <t xml:space="preserve">Pause Squat</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3131,14 +3136,14 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Box+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pause+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pause Squat</t>
+          <t xml:space="preserve">Safety Bar Squat</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3153,14 +3158,14 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pause+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Safety+Bar+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Safety Bar Squat</t>
+          <t xml:space="preserve">Smith Machine Squat</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3175,14 +3180,14 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Safety+Bar+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Smith+Machine+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smith Machine Squat</t>
+          <t xml:space="preserve">Belt Squat</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3197,14 +3202,14 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Smith+Machine+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Belt+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Belt Squat</t>
+          <t xml:space="preserve">Hack Squat</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3219,14 +3224,14 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Belt+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hack+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hack Squat</t>
+          <t xml:space="preserve">Machine Hack Squat</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3241,14 +3246,14 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hack+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Hack+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine Hack Squat</t>
+          <t xml:space="preserve">Pendulum Squat</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3263,14 +3268,14 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Hack+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pendulum+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pendulum Squat</t>
+          <t xml:space="preserve">Leg Press</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3285,14 +3290,14 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pendulum+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Leg+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leg Press</t>
+          <t xml:space="preserve">Single-Leg Press</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3307,14 +3312,14 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Leg+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single-Leg Press</t>
+          <t xml:space="preserve">Bulgarian Split Squat</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3329,14 +3334,14 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bulgarian+Split+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulgarian Split Squat</t>
+          <t xml:space="preserve">Split Squat</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3351,14 +3356,14 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bulgarian+Split+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Split+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Split Squat</t>
+          <t xml:space="preserve">Walking Lunge</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3373,14 +3378,14 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Split+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Walking+Lunge+proper+form</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walking Lunge</t>
+          <t xml:space="preserve">Reverse Lunge</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3395,14 +3400,14 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Walking+Lunge+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Lunge+proper+form</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reverse Lunge</t>
+          <t xml:space="preserve">Forward Lunge</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3417,14 +3422,14 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Lunge+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Forward+Lunge+proper+form</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forward Lunge</t>
+          <t xml:space="preserve">Lateral Lunge</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3439,14 +3444,14 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Forward+Lunge+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lateral+Lunge+proper+form</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lateral Lunge</t>
+          <t xml:space="preserve">Curtsy Lunge</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3461,14 +3466,14 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lateral+Lunge+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Curtsy+Lunge+proper+form</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Curtsy Lunge</t>
+          <t xml:space="preserve">Deficit Reverse Lunge</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3483,14 +3488,14 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Curtsy+Lunge+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Deficit+Reverse+Lunge+proper+form</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deficit Reverse Lunge</t>
+          <t xml:space="preserve">Step-Up</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3505,14 +3510,14 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Deficit+Reverse+Lunge+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Step-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Step-Up</t>
+          <t xml:space="preserve">Leg Extension</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3527,14 +3532,14 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Step-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Leg+Extension+proper+form</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leg Extension</t>
+          <t xml:space="preserve">Single-Leg Extension</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3549,14 +3554,14 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Leg+Extension+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Extension+proper+form</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single-Leg Extension</t>
+          <t xml:space="preserve">Sissy Squat</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3569,16 +3574,21 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Extension+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sissy+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sissy Squat</t>
+          <t xml:space="preserve">Wall Sit</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3598,19 +3608,24 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sissy+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wall+Sit+proper+form</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wall Sit</t>
+          <t xml:space="preserve">Romanian Deadlift</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quads</t>
+          <t xml:space="preserve">Hamstrings</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3618,26 +3633,16 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Wall+Sit+proper+form</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Romanian+Deadlift+proper+form</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Romanian Deadlift</t>
+          <t xml:space="preserve">Dumbbell Romanian Deadlift</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3652,14 +3657,14 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Romanian+Deadlift+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Romanian+Deadlift+proper+form</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dumbbell Romanian Deadlift</t>
+          <t xml:space="preserve">Single-Leg Romanian Deadlift</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3674,14 +3679,14 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dumbbell+Romanian+Deadlift+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Romanian+Deadlift+proper+form</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single-Leg Romanian Deadlift</t>
+          <t xml:space="preserve">Stiff-Leg Deadlift</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3696,14 +3701,14 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Romanian+Deadlift+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Stiff-Leg+Deadlift+proper+form</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stiff-Leg Deadlift</t>
+          <t xml:space="preserve">Lying Leg Curl</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3718,14 +3723,14 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Stiff-Leg+Deadlift+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lying+Leg+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lying Leg Curl</t>
+          <t xml:space="preserve">Seated Leg Curl</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3740,14 +3745,14 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lying+Leg+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Leg+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seated Leg Curl</t>
+          <t xml:space="preserve">Standing Leg Curl</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3762,14 +3767,14 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Leg+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Standing+Leg+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Standing Leg Curl</t>
+          <t xml:space="preserve">Nordic Curl</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3782,16 +3787,21 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Standing+Leg+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Nordic+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordic Curl</t>
+          <t xml:space="preserve">Glute-Ham Raise</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3804,21 +3814,16 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Nordic+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Glute-Ham+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glute-Ham Raise</t>
+          <t xml:space="preserve">Good Morning</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3833,14 +3838,14 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Glute-Ham+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Good+Morning+proper+form</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Good Morning</t>
+          <t xml:space="preserve">Back Extension</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3855,14 +3860,14 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Good+Morning+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Back+Extension+proper+form</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back Extension</t>
+          <t xml:space="preserve">45-Degree Back Extension</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3877,19 +3882,19 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Back+Extension+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=45-Degree+Back+Extension+proper+form</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">45-Degree Back Extension</t>
+          <t xml:space="preserve">Hip Thrust</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hamstrings</t>
+          <t xml:space="preserve">Glutes</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3899,14 +3904,14 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=45-Degree+Back+Extension+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hip+Thrust+proper+form</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hip Thrust</t>
+          <t xml:space="preserve">Barbell Hip Thrust</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -3921,14 +3926,14 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hip+Thrust+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Hip+Thrust+proper+form</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barbell Hip Thrust</t>
+          <t xml:space="preserve">Single-Leg Hip Thrust</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -3943,14 +3948,14 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Barbell+Hip+Thrust+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Hip+Thrust+proper+form</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single-Leg Hip Thrust</t>
+          <t xml:space="preserve">Machine Hip Thrust</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -3965,14 +3970,14 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Hip+Thrust+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Hip+Thrust+proper+form</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine Hip Thrust</t>
+          <t xml:space="preserve">Glute Bridge</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3987,14 +3992,14 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Hip+Thrust+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Glute+Bridge+proper+form</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glute Bridge</t>
+          <t xml:space="preserve">Cable Kickback</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4009,14 +4014,14 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Glute+Bridge+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Kickback+proper+form</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Kickback</t>
+          <t xml:space="preserve">Machine Glute Kickback</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4031,14 +4036,14 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Kickback+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Glute+Kickback+proper+form</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine Glute Kickback</t>
+          <t xml:space="preserve">Cable Pull-Through</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4053,14 +4058,14 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Machine+Glute+Kickback+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Pull-Through+proper+form</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Pull-Through</t>
+          <t xml:space="preserve">Frog Pump</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4075,19 +4080,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Pull-Through+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Frog+Pump+proper+form</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frog Pump</t>
+          <t xml:space="preserve">Adductor Machine</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glutes</t>
+          <t xml:space="preserve">Adductors</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4097,14 +4102,14 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Frog+Pump+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Adductor+Machine+proper+form</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adductor Machine</t>
+          <t xml:space="preserve">Copenhagen Plank</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4117,16 +4122,26 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Adductor+Machine+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Copenhagen+Plank+proper+form</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copenhagen Plank</t>
+          <t xml:space="preserve">Sumo Squat</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4139,26 +4154,16 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Copenhagen+Plank+proper+form</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sumo+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sumo Squat</t>
+          <t xml:space="preserve">Cossack Squat</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4171,21 +4176,26 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sumo+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cossack+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cossack Squat</t>
+          <t xml:space="preserve">Abductor Machine</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adductors</t>
+          <t xml:space="preserve">Abductors</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4193,21 +4203,16 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cossack+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Abductor+Machine+proper+form</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abductor Machine</t>
+          <t xml:space="preserve">Cable Hip Abduction</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4222,14 +4227,14 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Abductor+Machine+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Hip+Abduction+proper+form</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Hip Abduction</t>
+          <t xml:space="preserve">Banded Lateral Walk</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4242,16 +4247,21 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Hip+Abduction+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Banded+Lateral+Walk+proper+form</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banded Lateral Walk</t>
+          <t xml:space="preserve">Clamshell</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4271,19 +4281,19 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Banded+Lateral+Walk+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Clamshell+proper+form</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clamshell</t>
+          <t xml:space="preserve">Standing Calf Raise</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abductors</t>
+          <t xml:space="preserve">Calves</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4291,21 +4301,16 @@
           <t xml:space="preserve">Legs</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Clamshell+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Standing+Calf+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Standing Calf Raise</t>
+          <t xml:space="preserve">Seated Calf Raise</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4320,14 +4325,14 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Standing+Calf+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Calf+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seated Calf Raise</t>
+          <t xml:space="preserve">Leg Press Calf Raise</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4342,14 +4347,14 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Seated+Calf+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Leg+Press+Calf+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leg Press Calf Raise</t>
+          <t xml:space="preserve">Smith Machine Calf Raise</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4364,14 +4369,14 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Leg+Press+Calf+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Smith+Machine+Calf+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smith Machine Calf Raise</t>
+          <t xml:space="preserve">Single-Leg Calf Raise</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4386,14 +4391,14 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Smith+Machine+Calf+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Calf+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single-Leg Calf Raise</t>
+          <t xml:space="preserve">Donkey Calf Raise</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4408,14 +4413,14 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Single-Leg+Calf+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Donkey+Calf+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Donkey Calf Raise</t>
+          <t xml:space="preserve">Tibialis Raise</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4430,36 +4435,46 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Donkey+Calf+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Tibialis+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tibialis Raise</t>
+          <t xml:space="preserve">Plank</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calves</t>
+          <t xml:space="preserve">Core</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legs</t>
+          <t xml:space="preserve">Core</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Tibialis+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Plank+proper+form</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plank</t>
+          <t xml:space="preserve">Side Plank</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4479,7 +4494,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Plank+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Side+Plank+proper+form</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -4491,7 +4506,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Side Plank</t>
+          <t xml:space="preserve">RKC Plank</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4511,7 +4526,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Side+Plank+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=RKC+Plank+proper+form</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -4523,7 +4538,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">RKC Plank</t>
+          <t xml:space="preserve">Hollow Body Hold</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4543,7 +4558,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=RKC+Plank+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hollow+Body+Hold+proper+form</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -4555,7 +4570,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollow Body Hold</t>
+          <t xml:space="preserve">Dead Bug</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4575,19 +4590,14 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hollow+Body+Hold+proper+form</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dead+Bug+proper+form</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dead Bug</t>
+          <t xml:space="preserve">Bird Dog</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4607,14 +4617,14 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dead+Bug+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bird+Dog+proper+form</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bird Dog</t>
+          <t xml:space="preserve">Hanging Leg Raise</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4634,14 +4644,14 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bird+Dog+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hanging+Leg+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanging Leg Raise</t>
+          <t xml:space="preserve">Hanging Knee Raise</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4661,14 +4671,14 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hanging+Leg+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hanging+Knee+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanging Knee Raise</t>
+          <t xml:space="preserve">Captain's Chair Leg Raise</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4688,14 +4698,14 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hanging+Knee+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Captain%27s+Chair+Leg+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Captain's Chair Leg Raise</t>
+          <t xml:space="preserve">Lying Leg Raise</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4715,14 +4725,14 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Captain%27s+Chair+Leg+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lying+Leg+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lying Leg Raise</t>
+          <t xml:space="preserve">Toes-to-Bar</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4742,14 +4752,14 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Lying+Leg+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Toes-to-Bar+proper+form</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toes-to-Bar</t>
+          <t xml:space="preserve">Dragon Flag</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4769,14 +4779,14 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Toes-to-Bar+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dragon+Flag+proper+form</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dragon Flag</t>
+          <t xml:space="preserve">V-Up</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4796,14 +4806,14 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Dragon+Flag+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=V-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">V-Up</t>
+          <t xml:space="preserve">Sit-Up</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4823,14 +4833,14 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=V-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sit-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sit-Up</t>
+          <t xml:space="preserve">Decline Sit-Up</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4850,14 +4860,14 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sit-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Decline+Sit-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decline Sit-Up</t>
+          <t xml:space="preserve">Crunch</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4877,14 +4887,14 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Decline+Sit-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Crunch+proper+form</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crunch</t>
+          <t xml:space="preserve">Bicycle Crunch</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4904,14 +4914,14 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Crunch+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bicycle+Crunch+proper+form</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bicycle Crunch</t>
+          <t xml:space="preserve">Reverse Crunch</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4931,14 +4941,14 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Bicycle+Crunch+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Crunch+proper+form</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reverse Crunch</t>
+          <t xml:space="preserve">Cable Crunch</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4951,21 +4961,16 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Reverse+Crunch+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Crunch+proper+form</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cable Crunch</t>
+          <t xml:space="preserve">Ab Wheel Rollout</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4980,14 +4985,14 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Cable+Crunch+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Ab+Wheel+Rollout+proper+form</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ab Wheel Rollout</t>
+          <t xml:space="preserve">Russian Twist</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5002,14 +5007,14 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Ab+Wheel+Rollout+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Russian+Twist+proper+form</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Russian Twist</t>
+          <t xml:space="preserve">Pallof Press</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5024,14 +5029,14 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Russian+Twist+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pallof+Press+proper+form</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pallof Press</t>
+          <t xml:space="preserve">Landmine Twist</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5046,14 +5051,14 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Pallof+Press+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Landmine+Twist+proper+form</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landmine Twist</t>
+          <t xml:space="preserve">Woodchopper</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5068,14 +5073,14 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Landmine+Twist+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Woodchopper+proper+form</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Woodchopper</t>
+          <t xml:space="preserve">Mountain Climber</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5088,16 +5093,26 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Woodchopper+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Mountain+Climber+proper+form</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mountain Climber</t>
+          <t xml:space="preserve">Farmer Carry</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5110,14 +5125,9 @@
           <t xml:space="preserve">Core</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Mountain+Climber+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Farmer+Carry+proper+form</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -5129,7 +5139,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farmer Carry</t>
+          <t xml:space="preserve">Suitcase Carry</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5144,7 +5154,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Farmer+Carry+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Suitcase+Carry+proper+form</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -5156,34 +5166,29 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suitcase Carry</t>
+          <t xml:space="preserve">Neck Curl</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
+          <t xml:space="preserve">Neck</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
           <t xml:space="preserve">Core</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Core</t>
-        </is>
-      </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Suitcase+Carry+proper+form</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Neck+Curl+proper+form</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neck Curl</t>
+          <t xml:space="preserve">Neck Extension</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5198,14 +5203,14 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Neck+Curl+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Neck+Extension+proper+form</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neck Extension</t>
+          <t xml:space="preserve">Neck Harness Raise</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5220,36 +5225,36 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Neck+Extension+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Neck+Harness+Raise+proper+form</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neck Harness Raise</t>
+          <t xml:space="preserve">Power Clean</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neck</t>
+          <t xml:space="preserve">Full body</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core</t>
+          <t xml:space="preserve">Full body</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Neck+Harness+Raise+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Power+Clean+proper+form</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power Clean</t>
+          <t xml:space="preserve">Hang Clean</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5264,14 +5269,14 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Power+Clean+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hang+Clean+proper+form</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hang Clean</t>
+          <t xml:space="preserve">Clean and Jerk</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5286,14 +5291,14 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hang+Clean+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Clean+and+Jerk+proper+form</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clean and Jerk</t>
+          <t xml:space="preserve">Snatch</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5308,14 +5313,14 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Clean+and+Jerk+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Snatch+proper+form</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snatch</t>
+          <t xml:space="preserve">Power Snatch</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5330,14 +5335,14 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Snatch+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Power+Snatch+proper+form</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power Snatch</t>
+          <t xml:space="preserve">Hang Snatch</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5352,14 +5357,14 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Power+Snatch+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hang+Snatch+proper+form</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hang Snatch</t>
+          <t xml:space="preserve">Clean Pull</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5374,14 +5379,14 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Hang+Snatch+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Clean+Pull+proper+form</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clean Pull</t>
+          <t xml:space="preserve">Snatch Pull</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5396,14 +5401,14 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Clean+Pull+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Snatch+Pull+proper+form</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snatch Pull</t>
+          <t xml:space="preserve">Overhead Squat</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5418,14 +5423,14 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Snatch+Pull+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Overhead+Squat+proper+form</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overhead Squat</t>
+          <t xml:space="preserve">Thruster</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5440,14 +5445,14 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Overhead+Squat+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Thruster+proper+form</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thruster</t>
+          <t xml:space="preserve">Kettlebell Swing</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5462,14 +5467,14 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Thruster+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Kettlebell+Swing+proper+form</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettlebell Swing</t>
+          <t xml:space="preserve">Kettlebell Clean</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5484,14 +5489,14 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Kettlebell+Swing+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Kettlebell+Clean+proper+form</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettlebell Clean</t>
+          <t xml:space="preserve">Kettlebell Snatch</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5506,14 +5511,14 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Kettlebell+Clean+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Kettlebell+Snatch+proper+form</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kettlebell Snatch</t>
+          <t xml:space="preserve">Turkish Get-Up</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5528,14 +5533,14 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Kettlebell+Snatch+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Turkish+Get-Up+proper+form</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turkish Get-Up</t>
+          <t xml:space="preserve">Burpee</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5548,16 +5553,21 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Turkish+Get-Up+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Burpee+proper+form</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Burpee</t>
+          <t xml:space="preserve">Man Maker</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5570,21 +5580,16 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Burpee+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Man+Maker+proper+form</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Man Maker</t>
+          <t xml:space="preserve">Sled Push</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5599,14 +5604,19 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Man+Maker+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sled+Push+proper+form</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sled Push</t>
+          <t xml:space="preserve">Sled Pull</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5621,7 +5631,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sled+Push+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sled+Pull+proper+form</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -5633,7 +5643,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sled Pull</t>
+          <t xml:space="preserve">Battle Ropes</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5646,9 +5656,14 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sled+Pull+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Battle+Ropes+proper+form</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -5660,7 +5675,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Battle Ropes</t>
+          <t xml:space="preserve">Box Jump</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5680,19 +5695,14 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Battle+Ropes+proper+form</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Box+Jump+proper+form</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Jump</t>
+          <t xml:space="preserve">Broad Jump</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5712,14 +5722,14 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Box+Jump+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Broad+Jump+proper+form</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Broad Jump</t>
+          <t xml:space="preserve">Medicine Ball Slam</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5732,21 +5742,16 @@
           <t xml:space="preserve">Full body</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Broad+Jump+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Medicine+Ball+Slam+proper+form</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medicine Ball Slam</t>
+          <t xml:space="preserve">Medicine Ball Chest Pass</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5761,36 +5766,46 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Medicine+Ball+Slam+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Medicine+Ball+Chest+Pass+proper+form</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medicine Ball Chest Pass</t>
+          <t xml:space="preserve">Rowing Machine</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full body</t>
+          <t xml:space="preserve">Conditioning</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Full body</t>
+          <t xml:space="preserve">Conditioning</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Medicine+Ball+Chest+Pass+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Rowing+Machine+proper+form</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rowing Machine</t>
+          <t xml:space="preserve">Assault Bike</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5810,7 +5825,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Rowing+Machine+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Assault+Bike+proper+form</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -5822,7 +5837,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assault Bike</t>
+          <t xml:space="preserve">Ski Erg</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5842,7 +5857,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Assault+Bike+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Ski+Erg+proper+form</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -5854,7 +5869,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ski Erg</t>
+          <t xml:space="preserve">Treadmill Run</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5874,7 +5889,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Ski+Erg+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Treadmill+Run+proper+form</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -5886,7 +5901,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Treadmill Run</t>
+          <t xml:space="preserve">Incline Treadmill Walk</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5906,7 +5921,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Treadmill+Run+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Treadmill+Walk+proper+form</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -5918,7 +5933,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Incline Treadmill Walk</t>
+          <t xml:space="preserve">Stationary Bike</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5938,7 +5953,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Incline+Treadmill+Walk+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Stationary+Bike+proper+form</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -5950,7 +5965,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationary Bike</t>
+          <t xml:space="preserve">Stair Climber</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5970,7 +5985,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Stationary+Bike+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Stair+Climber+proper+form</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -5982,7 +5997,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stair Climber</t>
+          <t xml:space="preserve">Elliptical</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6002,7 +6017,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Stair+Climber+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Elliptical+proper+form</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -6014,7 +6029,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elliptical</t>
+          <t xml:space="preserve">Jump Rope</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6034,7 +6049,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Elliptical+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Jump+Rope+proper+form</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -6046,7 +6061,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jump Rope</t>
+          <t xml:space="preserve">Sprint Interval</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6066,42 +6081,10 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Jump+Rope+proper+form</t>
+          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sprint+Interval+proper+form</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sprint Interval</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conditioning</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conditioning</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.youtube.com/results?search_query=Sprint+Interval+proper+form</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>

--- a/docs/download/training-tracker-template.xlsx
+++ b/docs/download/training-tracker-template.xlsx
@@ -60,6 +60,11 @@
           <t xml:space="preserve">Notes</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Group</t>
+        </is>
+      </c>
     </row>
   </sheetData>
 </worksheet>
@@ -6128,6 +6133,11 @@
           <t xml:space="preserve">include in new session</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">group</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6238,6 +6248,11 @@
       <c r="E6">
         <v>0</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6258,6 +6273,11 @@
       </c>
       <c r="E7">
         <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
       </c>
     </row>
     <row r="8">

--- a/docs/download/training-tracker-template.xlsx
+++ b/docs/download/training-tracker-template.xlsx
@@ -65,6 +65,11 @@
           <t xml:space="preserve">Group</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drop set</t>
+        </is>
+      </c>
     </row>
   </sheetData>
 </worksheet>
